--- a/artfynd/A 47707-2023 artfynd.xlsx
+++ b/artfynd/A 47707-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47707-2023 artfynd.xlsx
+++ b/artfynd/A 47707-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98417205</v>
+        <v>112998921</v>
       </c>
       <c r="B2" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681727.8587501025</v>
+        <v>681732</v>
       </c>
       <c r="R2" t="n">
-        <v>6566222.255700057</v>
+        <v>6566234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,71 +766,81 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Jonsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Elin Jonsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>AKN0133 Norrbyskogen</t>
-        </is>
-      </c>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112984762</v>
+        <v>113418569</v>
       </c>
       <c r="B3" t="n">
-        <v>91313</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vendelsö (Vendelsö), Srm</t>
+          <t>Norrbyskogen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681760</v>
+        <v>681826</v>
       </c>
       <c r="R3" t="n">
-        <v>6566106</v>
+        <v>6566196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,31 +893,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112998921</v>
+        <v>113418570</v>
       </c>
       <c r="B4" t="n">
-        <v>93852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681733</v>
+        <v>681836</v>
       </c>
       <c r="R4" t="n">
-        <v>6566234</v>
+        <v>6566188</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,12 +1028,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,55 +1051,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112998922</v>
+        <v>112984762</v>
       </c>
       <c r="B5" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrbyskogen, Srm</t>
+          <t>Vendelsö, Vendelsö, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681727</v>
+        <v>681761</v>
       </c>
       <c r="R5" t="n">
-        <v>6566226</v>
+        <v>6566105</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,91 +1143,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig gran.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig gran.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113418566</v>
+        <v>113418562</v>
       </c>
       <c r="B6" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrbyskogen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681793</v>
+        <v>681702</v>
       </c>
       <c r="R6" t="n">
-        <v>6566176</v>
+        <v>6566286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,24 +1251,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Levande grov gran.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande grov gran.</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1310,15 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113418569</v>
+        <v>98417205</v>
       </c>
       <c r="B7" t="n">
-        <v>94179</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1350,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681826</v>
+        <v>681728</v>
       </c>
       <c r="R7" t="n">
-        <v>6566196</v>
+        <v>6566223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,22 +1336,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,34 +1352,530 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>AKN0133 Norrbyskogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112998922</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrbyskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>681727</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6566226</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig gran.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig gran.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113418566</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrbyskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>681793</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6566176</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Levande grov gran.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande grov gran.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113418568</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrbyskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>681811</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6566183</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-10-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Klen granlåga med bark kvar.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga med bark kvar.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>73075716</v>
+      </c>
+      <c r="B11" t="n">
+        <v>40269</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>214815</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Större träfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cossus cossus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gudöbroleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>681790</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6566025</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-08-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-08-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Irja Hedman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Irja Hedman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47707-2023 artfynd.xlsx
+++ b/artfynd/A 47707-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998921</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418569</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418570</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112984762</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418562</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
           <t>AKN0133 Norrbyskogen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98417205</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112998922</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1633,6 +1673,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1765,6 +1810,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418568</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1876,8 +1926,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73075716</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>